--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0036.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0036.xlsx
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Chắc chắn rồi.</t>
+          <t>Được thôi.</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Cậu cũng cảm nhận được tần số bất thường đó à?</t>
+          <t>Mày cũng cảm nhận được tần số bất thường đó à?</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Đây là lần thứ bảy ta thấy hắn ngã ở đó rồi.</t>
+          <t>Đây là lần thứ bảy tao thấy hắn ngã ở đó rồi.</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Con mèo đó nằm đó đã hai tháng rồi... có khi còn lâu hơn. Ta mới biết nó có hai tháng thôi.</t>
+          <t>Con mèo đó nằm đó đã hai tháng rồi... có khi còn lâu hơn. Tao mới biết nó có hai tháng thôi.</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Ta nghĩ nó giống như... một cuộc gọi không có hồi đáp.</t>
+          <t>Tao nghĩ nó giống như... một cuộc gọi không có hồi đáp.</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>...Không phải ta ghét họ. Chỉ là mọi thứ... quá bình thường. Họ có công việc, ta có trường lớp. Chúng ta hầu như chẳng bao giờ ở bên nhau.</t>
+          <t>...Không phải tao ghét họ. Chỉ là mọi thứ... quá bình thường. Họ có công việc, tao có trường lớp. Chúng tao hầu như chẳng bao giờ ở bên nhau.</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Chisa—! Cậu—!</t>
+          <t>Chisa—! bạn—!</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Ở quê ta, Cộng Hưởng Giả không được chấp nhận. Ai không kiểm soát được năng lực thì như quả bom hẹn giờ... bị sợ hãi và căm ghét.</t>
+          <t>Ở quê tao, Resonator không được chấp nhận. Ai không kiểm soát được năng lực thì như quả bom hẹn giờ... bị sợ hãi và căm ghét.</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Sau khi trở thành Cộng Hưởng Giả và bị giám sát, những cơ hội ấy càng hiếm hoi hơn. Ta nghĩ những lời đồn về ta cũng đã gây áp lực không nhỏ lên họ.</t>
+          <t>Sau khi trở thành Resonator và bị giám sát, những cơ hội ấy càng hiếm hoi hơn. Ta nghĩ những lời đồn về ta cũng đã gây áp lực không nhỏ lên họ.</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Vậy là cậu đã xuất hiện.</t>
+          <t>Vậy là mày đã xuất hiện.</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Ừ... xương cốt ta đang run lên đây này!</t>
+          <t>Ừ... xương cốt tao đang run lên đây này!</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>?i? ra?!</t>
+          <t>Cút… ra—!</t>
         </is>
       </c>
     </row>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>?i ra?</t>
+          <t>Cút ra—</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9806,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>?I RA NGAY?!!</t>
+          <t>CÚT RA NGAY—!!</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>{PlayerName}, ta có chuyện muốn nói với cậu. Nhưng… có khi chỉ là ta tưởng tượng thôi.</t>
+          <t>{PlayerName}, tao có chuyện muốn nói với cậu. Nhưng… có khi chỉ là tao tưởng tượng thôi.</t>
         </is>
       </c>
     </row>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Cậu tìm thấy gì?</t>
+          <t>Ngươi tìm thấy gì?</t>
         </is>
       </c>
     </row>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Có lẽ. Nghe nói cô ấy là Cộng Hưởng Giả bị giám sát... Tốt nhất là tránh xa ra.</t>
+          <t>Có lẽ. Nghe nói cô ấy là Resonator bị giám sát... Tốt nhất là tránh xa ra.</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>QUAY LẠI ĐI, NẮM TAY Ta NÀO!</t>
+          <t>QUAY LẠI ĐI, NẮM TAY TAO NÀO!</t>
         </is>
       </c>
     </row>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Cậu cần thời gian để chấp nhận rằng họ đã ra đi rồi.</t>
+          <t>Mày cần thời gian để chấp nhận rằng họ đã ra đi rồi.</t>
         </is>
       </c>
     </row>
@@ -18256,7 +18256,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Cậu cần thời gian để chấp nhận những gì đã thay đổi.</t>
+          <t>Mày cần thời gian để chấp nhận những gì đã thay đổi.</t>
         </is>
       </c>
     </row>
@@ -18451,7 +18451,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Không còn lựa chọn nào khác, ta phải đối mặt thôi... Đi nào.</t>
+          <t>Không còn lựa chọn nào khác, tao phải đối mặt thôi... Đi nào.</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -24565,7 +24565,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Đừng bảo lại là mấy Cộng Hưởng Giả đó nữa...</t>
+          <t>Đừng bảo lại là mấy Resonator đó nữa...</t>
         </is>
       </c>
     </row>
@@ -25475,7 +25475,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Kết luận... việc giám sát chặt chẽ Cộng Hưởng Giả là cần thiết để đảm bảo sự ổn định của xã hội...</t>
+          <t>Kết luận... việc giám sát chặt chẽ Resonator là cần thiết để đảm bảo sự ổn định của xã hội...</t>
         </is>
       </c>
     </row>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Ta thấy thương bố mẹ nó quá.</t>
+          <t>Tao thấy thương bố mẹ nó quá.</t>
         </is>
       </c>
     </row>
@@ -27880,7 +27880,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Thực ra ta định nghỉ việc vào tháng sau...</t>
+          <t>Thực ra tao định nghỉ việc vào tháng sau...</t>
         </is>
       </c>
     </row>
@@ -28920,7 +28920,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Chỉ nghĩ đến công việc thôi đã thấy phát ngán rồi. Nhưng hôm nay là sinh nhật con gái, nên ta phải về sớm. Không tăng ca đâu.</t>
+          <t>Chỉ nghĩ đến công việc thôi đã thấy phát ngán rồi. Nhưng hôm nay là sinh nhật con gái, nên tao phải về sớm. Không tăng ca đâu.</t>
         </is>
       </c>
     </row>
@@ -29830,7 +29830,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>K-Kỳ lạ ạ? Cháu không hiểu ý cậu là sao... Với cháu thì mọi thứ vẫn bình thường mà.</t>
+          <t>K-Kỳ lạ ạ? Cháu không hiểu ý bạn là sao... Với cháu thì mọi thứ vẫn bình thường mà.</t>
         </is>
       </c>
     </row>
@@ -30545,7 +30545,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Ta phải nói bao nhiêu lần nữa chứ? Đâu phải lỗi ta! Ta làm xong phần của mình rồi! Thế sao mọi thứ lại đổ hết lên đầu ta? Alo? Này!</t>
+          <t>Tao phải nói bao nhiêu lần nữa chứ? Đâu phải lỗi tao! Tao làm xong phần của mình rồi! Thế sao mọi thứ lại đổ hết lên đầu tao? Alo? Này!</t>
         </is>
       </c>
     </row>
